--- a/data/trans_dic/P57B_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P57B_R-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con bienestar emocional por debajo del percentil 15 (Bericat)</t>
+          <t>Población con peor bienestar socioemocional (percentil 15) (Bericat) (tasa de respuesta: 98,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,35; 17,66</t>
+          <t>12,13; 17,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,17; 20,52</t>
+          <t>16,16; 20,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,79; 18,27</t>
+          <t>14,84; 18,26</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 10,46</t>
+          <t>4,0; 10,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,13; 17,92</t>
+          <t>14,16; 17,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,87; 13,28</t>
+          <t>7,42; 13,31</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,28; 7,76</t>
+          <t>4,0; 7,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,25; 8,95</t>
+          <t>3,19; 9,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 7,65</t>
+          <t>3,89; 7,67</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,98; 12,92</t>
+          <t>9,19; 13,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,53; 16,77</t>
+          <t>11,77; 16,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,52; 14,62</t>
+          <t>11,37; 14,46</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,44; 10,69</t>
+          <t>7,46; 10,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,05; 14,98</t>
+          <t>11,04; 14,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,85; 12,48</t>
+          <t>10,04; 12,56</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con bienestar emocional por debajo del percentil 15 (Bericat)</t>
+          <t>Población con peor bienestar socioemocional (percentil 15) (Bericat) (tasa de respuesta: 98,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>77152; 110324</t>
+          <t>75783; 110277</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>106307; 134882</t>
+          <t>106241; 134696</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>189629; 234206</t>
+          <t>190247; 234129</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>47226; 124003</t>
+          <t>47484; 122917</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>133102; 168762</t>
+          <t>133372; 168103</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>167501; 282571</t>
+          <t>157969; 283306</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>59298</t>
+          <t>59299</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>29582; 53671</t>
+          <t>27689; 52925</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30056; 82643</t>
+          <t>29434; 83873</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>62064; 123497</t>
+          <t>62835; 123938</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>82155; 118175</t>
+          <t>84013; 119749</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>124451; 180963</t>
+          <t>127083; 181355</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>229774; 291510</t>
+          <t>226789; 288200</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>254253; 365385</t>
+          <t>254826; 366914</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>397967; 539590</t>
+          <t>397866; 534397</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>691136; 875819</t>
+          <t>704388; 881414</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57B_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P57B_R-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,13; 17,65</t>
+          <t>12,22; 17,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,16; 20,49</t>
+          <t>15,86; 20,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,84; 18,26</t>
+          <t>14,74; 17,87</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,0; 10,37</t>
+          <t>8,17; 11,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,16; 17,85</t>
+          <t>14,21; 17,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,42; 13,31</t>
+          <t>11,81; 14,52</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 7,65</t>
+          <t>4,14; 7,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,19; 9,08</t>
+          <t>6,96; 10,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,89; 7,67</t>
+          <t>5,94; 8,52</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,19; 13,1</t>
+          <t>9,47; 13,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,77; 16,8</t>
+          <t>14,15; 17,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,37; 14,46</t>
+          <t>12,56; 15,15</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,46; 10,74</t>
+          <t>9,24; 11,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,04; 14,83</t>
+          <t>13,77; 15,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,04; 12,56</t>
+          <t>11,89; 13,27</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>92287</t>
+          <t>99269</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>119989</t>
+          <t>127298</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>212276</t>
+          <t>226568</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>75783; 110277</t>
+          <t>82974; 117258</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>106241; 134696</t>
+          <t>113184; 143604</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>190247; 234129</t>
+          <t>205369; 248877</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>91874</t>
+          <t>102423</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>149533</t>
+          <t>169593</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>241407</t>
+          <t>272016</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>47484; 122917</t>
+          <t>85029; 122338</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>133372; 168103</t>
+          <t>149731; 189457</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>157969; 283306</t>
+          <t>247437; 304108</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39198</t>
+          <t>44186</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>59299</t>
+          <t>69090</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98496</t>
+          <t>113276</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27689; 52925</t>
+          <t>32496; 61185</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29434; 83873</t>
+          <t>55751; 86451</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>62835; 123938</t>
+          <t>94277; 135261</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>100269</t>
+          <t>110033</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>158662</t>
+          <t>175551</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>258931</t>
+          <t>285584</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>84013; 119749</t>
+          <t>92611; 131123</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>127083; 181355</t>
+          <t>155943; 197688</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>226789; 288200</t>
+          <t>261168; 315018</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>323628</t>
+          <t>355911</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>487482</t>
+          <t>541532</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>811110</t>
+          <t>897443</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>254826; 366914</t>
+          <t>321937; 393887</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>397866; 534397</t>
+          <t>505520; 575781</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>704388; 881414</t>
+          <t>850906; 949298</t>
         </is>
       </c>
     </row>
